--- a/packages/filen-web/src/tests/fixtures/spreadsheet/excel_full.xlsx
+++ b/packages/filen-web/src/tests/fixtures/spreadsheet/excel_full.xlsx
@@ -22,7 +22,7 @@
 <file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
 <comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="xr">
   <authors>
-    <author>Jan</author>
+    <author>Example Author</author>
   </authors>
   <commentList>
     <comment ref="B2" authorId="0" shapeId="0" xr:uid="{11111111-2222-3333-4444-555555555555}">
@@ -35,7 +35,7 @@
             <rFont val="Tahoma"/>
             <family val="2"/>
           </rPr>
-          <t>Jan:</t>
+          <t>Example Author:</t>
         </r>
         <r>
           <rPr>
